--- a/data/extracted/inventory-receipts/CONTENEDOR FRIA 240 20 FEBRERO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR FRIA 240 20 FEBRERO.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1926FC2-2983-4B9F-9B72-0581AA9D2216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3977,7 +3990,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -4018,11 +4031,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4303,50 +4315,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L1017"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4384,12 +4396,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4427,7 +4439,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4465,7 +4477,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4503,7 +4515,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4541,7 +4553,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4579,7 +4591,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4617,7 +4629,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4655,7 +4667,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4693,7 +4705,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4731,7 +4743,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4769,7 +4781,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4807,7 +4819,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4845,7 +4857,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4883,7 +4895,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4921,7 +4933,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4959,7 +4971,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4997,7 +5009,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -5035,7 +5047,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -5073,7 +5085,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -5111,7 +5123,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -5149,7 +5161,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -5187,7 +5199,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -5225,7 +5237,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5263,7 +5275,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5301,7 +5313,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5339,7 +5351,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5377,7 +5389,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5453,7 +5465,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5491,7 +5503,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5529,7 +5541,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5567,7 +5579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5605,7 +5617,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5643,7 +5655,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5681,7 +5693,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -5719,7 +5731,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -5757,7 +5769,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5795,7 +5807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5833,7 +5845,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5871,7 +5883,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5909,7 +5921,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5947,7 +5959,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5985,7 +5997,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -6023,7 +6035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -6061,7 +6073,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -6099,7 +6111,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -6137,7 +6149,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -6175,7 +6187,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -6213,7 +6225,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -6251,7 +6263,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6289,7 +6301,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6327,7 +6339,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6365,7 +6377,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6403,7 +6415,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6441,7 +6453,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6479,7 +6491,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -6517,7 +6529,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -6555,7 +6567,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6593,7 +6605,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -6631,7 +6643,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -6669,7 +6681,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F67" s="1" t="s">
         <v>145</v>
       </c>
@@ -6689,7 +6701,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F68" s="1" t="s">
         <v>147</v>
       </c>
@@ -6709,7 +6721,7 @@
         <v>1383.7</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6747,7 +6759,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6785,7 +6797,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6823,7 +6835,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6861,7 +6873,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6899,7 +6911,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6937,7 +6949,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6975,7 +6987,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -7013,7 +7025,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -7051,7 +7063,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -7089,7 +7101,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -7127,7 +7139,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -7165,7 +7177,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -7203,7 +7215,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -7241,7 +7253,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7279,7 +7291,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7317,7 +7329,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7355,7 +7367,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7393,7 +7405,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7431,7 +7443,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7469,7 +7481,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7507,7 +7519,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7545,7 +7557,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7583,7 +7595,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7621,7 +7633,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7659,7 +7671,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7697,7 +7709,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7735,7 +7747,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7773,7 +7785,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7811,7 +7823,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7849,7 +7861,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7887,7 +7899,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7925,7 +7937,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -7963,7 +7975,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -8001,7 +8013,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -8039,7 +8051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -8077,7 +8089,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -8115,7 +8127,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -8153,7 +8165,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8191,7 +8203,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -8229,7 +8241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8267,7 +8279,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8305,7 +8317,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8343,7 +8355,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8381,7 +8393,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8419,7 +8431,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8457,7 +8469,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8495,7 +8507,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8533,7 +8545,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8571,7 +8583,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8609,7 +8621,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8647,7 +8659,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8685,7 +8697,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8723,7 +8735,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8761,7 +8773,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8799,7 +8811,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8837,7 +8849,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8875,7 +8887,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8913,7 +8925,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8951,7 +8963,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8989,7 +9001,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -9027,7 +9039,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -9065,7 +9077,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -9103,7 +9115,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -9141,7 +9153,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -9179,7 +9191,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -9217,7 +9229,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9255,7 +9267,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9293,7 +9305,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9331,7 +9343,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9369,7 +9381,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9407,7 +9419,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9445,7 +9457,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9483,7 +9495,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9521,7 +9533,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9559,7 +9571,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9597,7 +9609,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9635,7 +9647,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9673,7 +9685,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9711,7 +9723,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9749,7 +9761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9787,7 +9799,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9825,7 +9837,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9863,7 +9875,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9901,7 +9913,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9939,7 +9951,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9977,7 +9989,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -10015,7 +10027,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -10053,7 +10065,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -10091,7 +10103,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -10129,7 +10141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -10167,7 +10179,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -10205,7 +10217,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -10243,7 +10255,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10281,7 +10293,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10319,7 +10331,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10357,7 +10369,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10395,7 +10407,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10433,7 +10445,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10471,7 +10483,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10509,7 +10521,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10547,7 +10559,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10585,7 +10597,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10623,7 +10635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10661,7 +10673,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10699,7 +10711,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10737,7 +10749,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10775,7 +10787,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10813,7 +10825,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10851,7 +10863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10889,7 +10901,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10927,7 +10939,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10965,7 +10977,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -11003,7 +11015,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -11041,7 +11053,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -11079,7 +11091,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -11117,7 +11129,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -11155,7 +11167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -11193,7 +11205,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -11231,7 +11243,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -11269,7 +11281,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -11307,7 +11319,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11345,7 +11357,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11383,7 +11395,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11421,7 +11433,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11459,7 +11471,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11497,7 +11509,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11535,7 +11547,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11573,7 +11585,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11611,7 +11623,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11649,7 +11661,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11687,7 +11699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11725,7 +11737,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11763,7 +11775,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11801,7 +11813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11839,7 +11851,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11877,7 +11889,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11915,7 +11927,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11953,7 +11965,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11991,7 +12003,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -12029,7 +12041,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -12067,7 +12079,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -12105,7 +12117,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F211" s="1" t="s">
         <v>145</v>
       </c>
@@ -12125,7 +12137,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F212" s="1" t="s">
         <v>375</v>
       </c>
@@ -12145,7 +12157,7 @@
         <v>3300.2</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -12183,7 +12195,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -12221,7 +12233,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -12259,7 +12271,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12297,7 +12309,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12335,7 +12347,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12373,7 +12385,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12411,7 +12423,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12449,7 +12461,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12487,7 +12499,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12525,7 +12537,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -12563,7 +12575,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -12601,7 +12613,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12639,7 +12651,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12677,7 +12689,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12715,7 +12727,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -12753,7 +12765,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -12791,7 +12803,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12829,7 +12841,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12867,7 +12879,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12905,7 +12917,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12943,7 +12955,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -12981,7 +12993,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -13019,7 +13031,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -13057,7 +13069,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -13095,7 +13107,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -13133,7 +13145,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -13171,7 +13183,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -13209,7 +13221,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -13247,7 +13259,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -13285,7 +13297,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13323,7 +13335,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13361,7 +13373,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -13399,7 +13411,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -13437,7 +13449,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13475,7 +13487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13513,7 +13525,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13551,7 +13563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13589,7 +13601,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13627,7 +13639,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -13665,7 +13677,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -13703,7 +13715,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13741,7 +13753,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13779,7 +13791,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13817,7 +13829,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -13855,7 +13867,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -13893,7 +13905,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -13931,7 +13943,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -13969,7 +13981,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -14007,7 +14019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -14045,7 +14057,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -14083,7 +14095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -14121,7 +14133,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -14159,7 +14171,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -14197,7 +14209,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -14235,7 +14247,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -14273,7 +14285,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -14311,7 +14323,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -14349,7 +14361,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14387,7 +14399,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14425,7 +14437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14463,7 +14475,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14501,7 +14513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14539,7 +14551,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14577,7 +14589,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14615,7 +14627,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14653,7 +14665,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14691,7 +14703,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14729,7 +14741,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14767,7 +14779,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14805,7 +14817,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14843,7 +14855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14881,7 +14893,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14919,7 +14931,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14957,7 +14969,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14995,7 +15007,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -15033,7 +15045,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -15071,7 +15083,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -15109,7 +15121,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -15147,7 +15159,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -15185,7 +15197,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -15223,7 +15235,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -15261,7 +15273,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F295" s="1" t="s">
         <v>145</v>
       </c>
@@ -15281,7 +15293,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F296" s="1" t="s">
         <v>1313</v>
       </c>
@@ -15300,7 +15312,7 @@
         <v>1868.1</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15338,7 +15350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15376,7 +15388,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15414,7 +15426,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15452,7 +15464,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15490,7 +15502,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15528,7 +15540,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15566,7 +15578,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15604,7 +15616,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15642,7 +15654,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15680,7 +15692,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15718,7 +15730,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15756,7 +15768,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15794,7 +15806,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15832,7 +15844,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15870,7 +15882,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15908,7 +15920,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15946,7 +15958,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15984,7 +15996,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -16022,7 +16034,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -16060,7 +16072,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -16098,7 +16110,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -16136,7 +16148,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -16174,7 +16186,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -16212,7 +16224,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -16250,7 +16262,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -16288,7 +16300,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16326,7 +16338,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16364,7 +16376,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16402,7 +16414,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16440,7 +16452,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16478,7 +16490,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16516,7 +16528,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16554,7 +16566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16592,7 +16604,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16630,7 +16642,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16668,7 +16680,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16706,7 +16718,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16744,7 +16756,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16782,7 +16794,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16820,7 +16832,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16858,7 +16870,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16896,7 +16908,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F339" s="1" t="s">
         <v>145</v>
       </c>
@@ -16916,7 +16928,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F340" s="1" t="s">
         <v>506</v>
       </c>
@@ -16936,7 +16948,7 @@
         <v>972.5</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -16974,7 +16986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -17012,7 +17024,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -17050,7 +17062,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -17088,7 +17100,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -17126,7 +17138,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -17164,7 +17176,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -17202,7 +17214,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -17240,7 +17252,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17278,7 +17290,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -17316,7 +17328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -17354,7 +17366,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17392,7 +17404,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17430,7 +17442,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17468,7 +17480,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17506,7 +17518,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17544,7 +17556,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17582,7 +17594,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17620,7 +17632,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17658,7 +17670,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17696,7 +17708,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17734,7 +17746,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17772,7 +17784,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17810,7 +17822,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17848,7 +17860,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17886,7 +17898,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17924,7 +17936,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17962,7 +17974,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -18000,7 +18012,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -18038,7 +18050,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -18076,7 +18088,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -18114,7 +18126,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -18152,7 +18164,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -18190,7 +18202,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -18228,7 +18240,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -18266,7 +18278,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18304,7 +18316,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18342,7 +18354,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18380,7 +18392,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18418,7 +18430,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>19</v>
       </c>
@@ -18456,7 +18468,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -18494,7 +18506,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18532,7 +18544,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18570,7 +18582,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18608,7 +18620,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18646,7 +18658,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18684,7 +18696,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18722,7 +18734,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18760,7 +18772,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18798,7 +18810,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18836,7 +18848,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18874,7 +18886,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18912,7 +18924,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18950,7 +18962,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18988,7 +19000,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -19026,7 +19038,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -19064,7 +19076,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -19102,7 +19114,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -19140,7 +19152,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -19178,7 +19190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -19216,7 +19228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -19254,7 +19266,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -19292,7 +19304,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19330,7 +19342,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19368,7 +19380,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19406,7 +19418,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19444,7 +19456,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19482,7 +19494,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19520,7 +19532,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19558,7 +19570,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19596,7 +19608,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19634,7 +19646,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19672,7 +19684,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19710,7 +19722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19748,7 +19760,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19786,7 +19798,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19824,7 +19836,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19862,7 +19874,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19900,7 +19912,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19938,7 +19950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19976,7 +19988,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -20014,7 +20026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -20052,7 +20064,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -20090,7 +20102,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -20128,7 +20140,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -20166,7 +20178,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -20204,7 +20216,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -20242,7 +20254,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -20280,7 +20292,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20318,7 +20330,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20356,7 +20368,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20394,7 +20406,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20432,7 +20444,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20470,7 +20482,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20508,7 +20520,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20546,7 +20558,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20584,7 +20596,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20622,7 +20634,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -20660,7 +20672,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -20698,7 +20710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20736,7 +20748,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20774,7 +20786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -20812,7 +20824,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -20850,7 +20862,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20888,7 +20900,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20926,7 +20938,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20964,7 +20976,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -21002,7 +21014,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -21040,7 +21052,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -21078,7 +21090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -21116,7 +21128,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -21154,7 +21166,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -21192,7 +21204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -21230,7 +21242,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -21268,7 +21280,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -21306,7 +21318,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -21344,7 +21356,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21382,7 +21394,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21420,7 +21432,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21458,7 +21470,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21496,7 +21508,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F461" s="1" t="s">
         <v>145</v>
       </c>
@@ -21516,7 +21528,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F462" s="1" t="s">
         <v>630</v>
       </c>
@@ -21536,7 +21548,7 @@
         <v>2735.6</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21574,7 +21586,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21612,7 +21624,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21650,7 +21662,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21688,7 +21700,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21726,7 +21738,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21764,7 +21776,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21802,7 +21814,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21840,7 +21852,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21878,7 +21890,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21916,7 +21928,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21954,7 +21966,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21992,7 +22004,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -22030,7 +22042,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -22068,7 +22080,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -22106,7 +22118,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -22144,7 +22156,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -22182,7 +22194,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -22220,7 +22232,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -22258,7 +22270,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -22296,7 +22308,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22334,7 +22346,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22372,7 +22384,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22410,7 +22422,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22448,7 +22460,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22486,7 +22498,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22524,7 +22536,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -22562,7 +22574,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -22600,7 +22612,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22638,7 +22650,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22676,7 +22688,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22714,7 +22726,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -22752,7 +22764,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -22790,7 +22802,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22828,7 +22840,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22866,7 +22878,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22904,7 +22916,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22942,7 +22954,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22980,7 +22992,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -23018,7 +23030,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -23056,7 +23068,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -23094,7 +23106,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -23132,7 +23144,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -23170,7 +23182,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -23208,7 +23220,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -23246,7 +23258,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -23284,7 +23296,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23322,7 +23334,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23360,7 +23372,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23398,7 +23410,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23436,7 +23448,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23474,7 +23486,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23512,7 +23524,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23550,7 +23562,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23588,7 +23600,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23626,7 +23638,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23664,7 +23676,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23702,7 +23714,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23740,7 +23752,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23778,7 +23790,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23816,7 +23828,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23854,7 +23866,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23892,7 +23904,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23930,7 +23942,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23968,7 +23980,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -24006,7 +24018,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -24044,7 +24056,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -24082,7 +24094,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -24120,7 +24132,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -24158,7 +24170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -24196,7 +24208,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -24234,7 +24246,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -24272,7 +24284,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -24310,7 +24322,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24348,7 +24360,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24386,7 +24398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24424,7 +24436,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24462,7 +24474,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24500,7 +24512,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24538,7 +24550,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24576,7 +24588,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24614,7 +24626,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24652,7 +24664,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24690,7 +24702,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F546" s="1" t="s">
         <v>145</v>
       </c>
@@ -24710,7 +24722,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F547" s="1" t="s">
         <v>717</v>
       </c>
@@ -24730,7 +24742,7 @@
         <v>1926.8</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24768,7 +24780,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24806,7 +24818,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24844,7 +24856,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24882,7 +24894,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24920,7 +24932,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24958,7 +24970,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24996,7 +25008,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -25034,7 +25046,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -25072,7 +25084,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -25110,7 +25122,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -25148,7 +25160,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -25186,7 +25198,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -25224,7 +25236,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -25262,7 +25274,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25300,7 +25312,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25338,7 +25350,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25376,7 +25388,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25414,7 +25426,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25452,7 +25464,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25490,7 +25502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25528,7 +25540,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25566,7 +25578,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25604,7 +25616,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25642,7 +25654,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25680,7 +25692,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25718,7 +25730,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25756,7 +25768,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25794,7 +25806,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25832,7 +25844,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25870,7 +25882,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25908,7 +25920,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25946,7 +25958,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25984,7 +25996,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -26022,7 +26034,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -26060,7 +26072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -26098,7 +26110,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -26136,7 +26148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -26174,7 +26186,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -26212,7 +26224,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -26250,7 +26262,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26288,7 +26300,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26326,7 +26338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26364,7 +26376,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26402,7 +26414,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26440,7 +26452,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26478,7 +26490,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26516,7 +26528,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26554,7 +26566,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26592,7 +26604,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26630,7 +26642,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -26668,7 +26680,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>19</v>
       </c>
@@ -26706,7 +26718,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26744,7 +26756,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26782,7 +26794,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26820,7 +26832,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26858,7 +26870,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26896,7 +26908,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26934,7 +26946,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26972,7 +26984,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -27010,7 +27022,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -27048,7 +27060,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -27086,7 +27098,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -27124,7 +27136,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -27162,7 +27174,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -27200,7 +27212,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -27238,7 +27250,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -27276,7 +27288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27314,7 +27326,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27352,7 +27364,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27390,7 +27402,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27428,7 +27440,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27466,7 +27478,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27504,7 +27516,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27542,7 +27554,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27580,7 +27592,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27618,7 +27630,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27656,7 +27668,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -27694,7 +27706,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>19</v>
       </c>
@@ -27732,7 +27744,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27770,7 +27782,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27808,7 +27820,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27846,7 +27858,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27884,7 +27896,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27922,7 +27934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27960,7 +27972,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27998,7 +28010,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -28036,7 +28048,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -28074,7 +28086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -28112,7 +28124,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -28150,7 +28162,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -28188,7 +28200,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -28226,7 +28238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -28264,7 +28276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28302,7 +28314,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28340,7 +28352,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28378,7 +28390,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28416,7 +28428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28454,7 +28466,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28492,7 +28504,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28530,7 +28542,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28568,7 +28580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28606,7 +28618,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28644,7 +28656,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28682,7 +28694,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28720,7 +28732,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28758,7 +28770,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28796,7 +28808,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28834,7 +28846,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28872,7 +28884,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28910,7 +28922,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28948,7 +28960,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28986,7 +28998,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -29024,7 +29036,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -29062,7 +29074,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -29100,7 +29112,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -29138,7 +29150,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -29176,7 +29188,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -29214,7 +29226,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -29252,7 +29264,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29290,7 +29302,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29328,7 +29340,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29366,7 +29378,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29404,7 +29416,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29442,7 +29454,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29480,7 +29492,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29518,7 +29530,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29556,7 +29568,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29594,7 +29606,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29632,7 +29644,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29670,7 +29682,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29708,7 +29720,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29746,7 +29758,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29784,7 +29796,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29822,7 +29834,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29860,7 +29872,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29898,7 +29910,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29936,7 +29948,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29974,7 +29986,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -30012,7 +30024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -30050,7 +30062,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -30088,7 +30100,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -30126,7 +30138,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -30164,7 +30176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -30202,7 +30214,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -30240,7 +30252,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30278,7 +30290,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>19</v>
       </c>
@@ -30316,7 +30328,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>19</v>
       </c>
@@ -30354,7 +30366,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30392,7 +30404,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30430,7 +30442,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30468,7 +30480,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30506,7 +30518,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30544,7 +30556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30582,7 +30594,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30620,7 +30632,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30658,7 +30670,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30696,7 +30708,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30734,7 +30746,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30772,7 +30784,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30810,7 +30822,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30848,7 +30860,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30886,7 +30898,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30924,7 +30936,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30962,7 +30974,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -31000,7 +31012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -31038,7 +31050,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -31076,7 +31088,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -31114,7 +31126,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -31152,7 +31164,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -31190,7 +31202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -31228,7 +31240,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -31266,7 +31278,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -31304,7 +31316,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31342,7 +31354,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31380,7 +31392,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31418,7 +31430,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31456,7 +31468,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31494,7 +31506,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31532,7 +31544,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31570,7 +31582,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31608,7 +31620,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31646,7 +31658,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31684,7 +31696,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>19</v>
       </c>
@@ -31722,7 +31734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -31760,7 +31772,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31798,7 +31810,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31836,7 +31848,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31874,7 +31886,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31912,7 +31924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31950,7 +31962,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31988,7 +32000,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -32026,7 +32038,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -32064,7 +32076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -32102,7 +32114,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -32140,7 +32152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -32178,7 +32190,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -32216,7 +32228,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -32254,7 +32266,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -32292,7 +32304,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -32330,7 +32342,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32368,7 +32380,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32406,7 +32418,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32444,7 +32456,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32482,7 +32494,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>19</v>
       </c>
@@ -32520,7 +32532,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>19</v>
       </c>
@@ -32558,7 +32570,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32596,7 +32608,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>19</v>
       </c>
@@ -32634,7 +32646,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>19</v>
       </c>
@@ -32672,7 +32684,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32710,7 +32722,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32748,7 +32760,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32786,7 +32798,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32824,7 +32836,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32862,7 +32874,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32900,7 +32912,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32938,7 +32950,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32976,7 +32988,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -33014,7 +33026,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -33052,7 +33064,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -33090,7 +33102,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -33128,7 +33140,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -33166,7 +33178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -33204,7 +33216,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>19</v>
       </c>
@@ -33242,7 +33254,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>19</v>
       </c>
@@ -33280,7 +33292,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -33318,7 +33330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -33356,7 +33368,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33394,7 +33406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33432,7 +33444,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33470,7 +33482,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33508,7 +33520,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33546,7 +33558,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33584,7 +33596,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33622,7 +33634,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33660,7 +33672,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>19</v>
       </c>
@@ -33698,7 +33710,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>19</v>
       </c>
@@ -33736,7 +33748,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33774,7 +33786,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33812,7 +33824,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33850,7 +33862,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33888,7 +33900,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33926,7 +33938,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33964,7 +33976,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>19</v>
       </c>
@@ -34002,7 +34014,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>19</v>
       </c>
@@ -34040,7 +34052,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -34078,7 +34090,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -34116,7 +34128,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>19</v>
       </c>
@@ -34154,7 +34166,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>19</v>
       </c>
@@ -34192,7 +34204,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -34230,7 +34242,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -34268,7 +34280,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -34306,7 +34318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -34344,7 +34356,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -34382,7 +34394,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -34420,7 +34432,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34458,7 +34470,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34496,7 +34508,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34534,7 +34546,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34572,7 +34584,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34610,7 +34622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34648,7 +34660,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34686,7 +34698,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34724,7 +34736,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34762,7 +34774,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34800,7 +34812,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34838,7 +34850,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34876,7 +34888,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34914,7 +34926,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34952,7 +34964,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34990,7 +35002,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -35028,7 +35040,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -35066,7 +35078,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -35104,7 +35116,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -35142,7 +35154,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -35180,7 +35192,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -35218,7 +35230,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -35256,7 +35268,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -35294,7 +35306,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -35332,7 +35344,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -35370,7 +35382,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F828" s="1" t="s">
         <v>145</v>
       </c>
@@ -35390,7 +35402,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F829" s="1" t="s">
         <v>1314</v>
       </c>
@@ -35407,7 +35419,7 @@
         <v>6671.4000000000024</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35445,7 +35457,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35483,7 +35495,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35521,7 +35533,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35559,7 +35571,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35597,7 +35609,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35635,7 +35647,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35673,7 +35685,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>19</v>
       </c>
@@ -35711,7 +35723,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>19</v>
       </c>
@@ -35749,7 +35761,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35787,7 +35799,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35825,7 +35837,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>19</v>
       </c>
@@ -35863,7 +35875,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>19</v>
       </c>
@@ -35901,7 +35913,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35939,7 +35951,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35977,7 +35989,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -36015,7 +36027,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -36053,7 +36065,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -36091,7 +36103,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -36129,7 +36141,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>19</v>
       </c>
@@ -36167,7 +36179,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>19</v>
       </c>
@@ -36205,7 +36217,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F851" s="1" t="s">
         <v>145</v>
       </c>
@@ -36225,7 +36237,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F852" s="1" t="s">
         <v>1163</v>
       </c>
@@ -36245,7 +36257,7 @@
         <v>477.9</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>19</v>
       </c>
@@ -36283,7 +36295,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>19</v>
       </c>
@@ -36321,7 +36333,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -36359,7 +36371,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36397,7 +36409,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36435,7 +36447,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36473,7 +36485,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36511,7 +36523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36549,7 +36561,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>19</v>
       </c>
@@ -36587,7 +36599,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>19</v>
       </c>
@@ -36625,7 +36637,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36663,7 +36675,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36701,7 +36713,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>19</v>
       </c>
@@ -36739,7 +36751,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>19</v>
       </c>
@@ -36777,7 +36789,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36815,7 +36827,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36853,7 +36865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36891,7 +36903,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36929,7 +36941,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36967,7 +36979,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -37005,7 +37017,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -37043,7 +37055,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -37081,7 +37093,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" s="1" t="s">
         <v>19</v>
       </c>
@@ -37119,7 +37131,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" s="1" t="s">
         <v>19</v>
       </c>
@@ -37157,7 +37169,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -37195,7 +37207,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -37233,7 +37245,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -37271,7 +37283,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -37309,7 +37321,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -37347,7 +37359,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37385,7 +37397,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37423,7 +37435,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37461,7 +37473,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37499,7 +37511,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37537,7 +37549,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37575,7 +37587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37613,7 +37625,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>19</v>
       </c>
@@ -37651,7 +37663,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>19</v>
       </c>
@@ -37689,7 +37701,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37727,7 +37739,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>19</v>
       </c>
@@ -37765,7 +37777,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>19</v>
       </c>
@@ -37803,7 +37815,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37841,7 +37853,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37879,7 +37891,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F896" s="1" t="s">
         <v>145</v>
       </c>
@@ -37899,7 +37911,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F897" s="1" t="s">
         <v>1315</v>
       </c>
@@ -37922,7 +37934,7 @@
         <v>996.10000000000025</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37960,7 +37972,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37998,7 +38010,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -38036,7 +38048,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -38074,7 +38086,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -38112,7 +38124,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -38150,7 +38162,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -38188,7 +38200,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -38226,7 +38238,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -38264,7 +38276,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>19</v>
       </c>
@@ -38302,7 +38314,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>19</v>
       </c>
@@ -38340,7 +38352,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -38378,7 +38390,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38416,7 +38428,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>19</v>
       </c>
@@ -38454,7 +38466,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>19</v>
       </c>
@@ -38492,7 +38504,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>19</v>
       </c>
@@ -38530,7 +38542,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>19</v>
       </c>
@@ -38568,7 +38580,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>19</v>
       </c>
@@ -38606,7 +38618,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>19</v>
       </c>
@@ -38644,7 +38656,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>19</v>
       </c>
@@ -38682,7 +38694,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>19</v>
       </c>
@@ -38720,7 +38732,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F919" s="1" t="s">
         <v>145</v>
       </c>
@@ -38740,7 +38752,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F920" s="1" t="s">
         <v>1163</v>
       </c>
@@ -38760,7 +38772,7 @@
         <v>491.7</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" s="1" t="s">
         <v>19</v>
       </c>
@@ -38798,7 +38810,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A922" s="1" t="s">
         <v>19</v>
       </c>
@@ -38836,7 +38848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" s="1" t="s">
         <v>19</v>
       </c>
@@ -38874,7 +38886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>19</v>
       </c>
@@ -38912,7 +38924,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A925" s="1" t="s">
         <v>19</v>
       </c>
@@ -38950,7 +38962,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A926" s="1" t="s">
         <v>19</v>
       </c>
@@ -38988,7 +39000,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" s="1" t="s">
         <v>19</v>
       </c>
@@ -39026,7 +39038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A928" s="1" t="s">
         <v>19</v>
       </c>
@@ -39064,7 +39076,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A929" s="1" t="s">
         <v>19</v>
       </c>
@@ -39102,7 +39114,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A930" s="1" t="s">
         <v>19</v>
       </c>
@@ -39140,7 +39152,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A931" s="1" t="s">
         <v>19</v>
       </c>
@@ -39178,7 +39190,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" s="1" t="s">
         <v>19</v>
       </c>
@@ -39216,7 +39228,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" s="1" t="s">
         <v>19</v>
       </c>
@@ -39254,7 +39266,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A934" s="1" t="s">
         <v>19</v>
       </c>
@@ -39292,7 +39304,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" s="1" t="s">
         <v>19</v>
       </c>
@@ -39330,7 +39342,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A936" s="1" t="s">
         <v>19</v>
       </c>
@@ -39368,7 +39380,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A937" s="1" t="s">
         <v>19</v>
       </c>
@@ -39406,7 +39418,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" s="1" t="s">
         <v>19</v>
       </c>
@@ -39444,7 +39456,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" s="1" t="s">
         <v>19</v>
       </c>
@@ -39482,7 +39494,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A940" s="1" t="s">
         <v>19</v>
       </c>
@@ -39520,7 +39532,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" s="1" t="s">
         <v>19</v>
       </c>
@@ -39558,7 +39570,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" s="1" t="s">
         <v>19</v>
       </c>
@@ -39596,7 +39608,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A943" s="1" t="s">
         <v>19</v>
       </c>
@@ -39634,7 +39646,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" s="1" t="s">
         <v>19</v>
       </c>
@@ -39672,7 +39684,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" s="1" t="s">
         <v>19</v>
       </c>
@@ -39710,7 +39722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A946" s="1" t="s">
         <v>19</v>
       </c>
@@ -39748,7 +39760,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" s="1" t="s">
         <v>19</v>
       </c>
@@ -39786,7 +39798,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A948" s="1" t="s">
         <v>19</v>
       </c>
@@ -39824,7 +39836,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A949" s="1" t="s">
         <v>19</v>
       </c>
@@ -39862,7 +39874,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" s="1" t="s">
         <v>19</v>
       </c>
@@ -39900,7 +39912,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A951" s="1" t="s">
         <v>19</v>
       </c>
@@ -39938,7 +39950,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A952" s="1" t="s">
         <v>19</v>
       </c>
@@ -39976,7 +39988,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A953" s="1" t="s">
         <v>19</v>
       </c>
@@ -40014,7 +40026,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A954" s="1" t="s">
         <v>19</v>
       </c>
@@ -40052,7 +40064,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A955" s="1" t="s">
         <v>19</v>
       </c>
@@ -40090,7 +40102,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" s="1" t="s">
         <v>19</v>
       </c>
@@ -40128,7 +40140,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A957" s="1" t="s">
         <v>19</v>
       </c>
@@ -40166,7 +40178,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A958" s="1" t="s">
         <v>19</v>
       </c>
@@ -40204,7 +40216,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" s="1" t="s">
         <v>19</v>
       </c>
@@ -40242,7 +40254,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A960" s="1" t="s">
         <v>19</v>
       </c>
@@ -40280,7 +40292,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A961" s="1" t="s">
         <v>19</v>
       </c>
@@ -40318,7 +40330,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" s="1" t="s">
         <v>19</v>
       </c>
@@ -40356,7 +40368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A963" s="1" t="s">
         <v>19</v>
       </c>
@@ -40394,7 +40406,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A964" s="1" t="s">
         <v>19</v>
       </c>
@@ -40432,7 +40444,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" s="1" t="s">
         <v>19</v>
       </c>
@@ -40470,7 +40482,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A966" s="1" t="s">
         <v>19</v>
       </c>
@@ -40508,7 +40520,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A967" s="1" t="s">
         <v>19</v>
       </c>
@@ -40546,7 +40558,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A968" s="1" t="s">
         <v>19</v>
       </c>
@@ -40584,7 +40596,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A969" s="1" t="s">
         <v>19</v>
       </c>
@@ -40622,7 +40634,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A970" s="1" t="s">
         <v>19</v>
       </c>
@@ -40660,7 +40672,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A971" s="1" t="s">
         <v>19</v>
       </c>
@@ -40698,7 +40710,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A972" s="1" t="s">
         <v>19</v>
       </c>
@@ -40736,7 +40748,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A973" s="1" t="s">
         <v>19</v>
       </c>
@@ -40774,7 +40786,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A974" s="1" t="s">
         <v>19</v>
       </c>
@@ -40812,7 +40824,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A975" s="1" t="s">
         <v>19</v>
       </c>
@@ -40850,7 +40862,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A976" s="1" t="s">
         <v>19</v>
       </c>
@@ -40888,7 +40900,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A977" s="1" t="s">
         <v>19</v>
       </c>
@@ -40926,7 +40938,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A978" s="1" t="s">
         <v>19</v>
       </c>
@@ -40964,7 +40976,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A979" s="1" t="s">
         <v>19</v>
       </c>
@@ -41002,7 +41014,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A980" s="1" t="s">
         <v>19</v>
       </c>
@@ -41040,7 +41052,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A981" s="1" t="s">
         <v>19</v>
       </c>
@@ -41078,7 +41090,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F982" s="1" t="s">
         <v>145</v>
       </c>
@@ -41098,7 +41110,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F983" s="1" t="s">
         <v>1298</v>
       </c>
@@ -41118,7 +41130,7 @@
         <v>1436.7</v>
       </c>
     </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F984" s="1" t="s">
         <v>145</v>
       </c>
@@ -41138,7 +41150,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A986" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41176,7 +41188,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F987" s="1" t="s">
         <v>145</v>
       </c>
@@ -41196,12 +41208,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K988" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A989" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41239,7 +41251,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F990" s="1" t="s">
         <v>145</v>
       </c>
@@ -41259,12 +41271,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K991" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A992" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41302,7 +41314,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F993" s="1" t="s">
         <v>145</v>
       </c>
@@ -41322,7 +41334,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J994" s="2" t="s">
         <v>26</v>
       </c>
@@ -41330,7 +41342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A995" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41368,7 +41380,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F996" s="1" t="s">
         <v>145</v>
       </c>
@@ -41388,12 +41400,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K997" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A998" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41431,7 +41443,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F999" s="1" t="s">
         <v>145</v>
       </c>
@@ -41451,12 +41463,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1000" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1000" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="1001" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1001" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41494,7 +41506,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="1002" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1002" s="1" t="s">
         <v>145</v>
       </c>
@@ -41514,12 +41526,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1003" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1003" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1004" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41557,7 +41569,7 @@
         <v>350.6</v>
       </c>
     </row>
-    <row r="1005" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1005" s="1" t="s">
         <v>145</v>
       </c>
@@ -41577,7 +41589,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1007" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1007" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41615,7 +41627,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="1008" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1008" s="1" t="s">
         <v>145</v>
       </c>
@@ -41635,7 +41647,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1009" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J1009" s="2" t="s">
         <v>26</v>
       </c>
@@ -41643,7 +41655,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="1010" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1010" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41681,7 +41693,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="1011" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1011" s="1" t="s">
         <v>145</v>
       </c>
@@ -41701,12 +41713,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1012" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1012" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="1013" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1013" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41744,7 +41756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="1014" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1014" s="1" t="s">
         <v>145</v>
       </c>
@@ -41764,12 +41776,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="1015" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1015" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="1016" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1016" s="1" t="s">
         <v>1299</v>
       </c>
@@ -41807,7 +41819,7 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1017" s="1" t="s">
         <v>145</v>
       </c>
@@ -41831,4 +41843,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{557B7AD7-99F6-489D-894A-98B10EDFC5D1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>